--- a/pmu-admissions-audit/deliverables_360/04_PMU_Admissions_Content_Review_Register_AR.xlsx
+++ b/pmu-admissions-audit/deliverables_360/04_PMU_Admissions_Content_Review_Register_AR.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>جاهزة للعرض الإداري (مسودة غير معتمدة)</t>
+          <t>معدّة للمراجعة الإدارية (غير معتمدة)</t>
         </is>
       </c>
     </row>
